--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,6 +2397,113 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122492226</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90791</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>883</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kärnticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Inocutis dryophila</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Berk.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norreda torp, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>662997</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6634280</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Känd lokal</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -2402,7 +2402,7 @@
         <v>122492226</v>
       </c>
       <c r="B15" t="n">
-        <v>90791</v>
+        <v>90796</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2416,11 +2416,6 @@
       </c>
       <c r="E15" t="n">
         <v>883</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Kärnticka</t>
-        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2402,7 +2402,7 @@
         <v>122492226</v>
       </c>
       <c r="B15" t="n">
-        <v>90796</v>
+        <v>90809</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2417,6 +2417,11 @@
       <c r="E15" t="n">
         <v>883</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kärnticka</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Inocutis dryophila</t>
@@ -2498,6 +2503,118 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122569536</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79950</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228430</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rostorangelav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Blastenia ferruginea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norredatorp, Norredatorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>662958</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6634243</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -2402,7 +2402,7 @@
         <v>122492226</v>
       </c>
       <c r="B15" t="n">
-        <v>90809</v>
+        <v>90822</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -2402,7 +2402,7 @@
         <v>122492226</v>
       </c>
       <c r="B15" t="n">
-        <v>90822</v>
+        <v>90816</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -2402,7 +2402,7 @@
         <v>122492226</v>
       </c>
       <c r="B15" t="n">
-        <v>90816</v>
+        <v>90817</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>122569536</v>
       </c>
       <c r="B16" t="n">
-        <v>79950</v>
+        <v>79951</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -2402,7 +2402,7 @@
         <v>122492226</v>
       </c>
       <c r="B15" t="n">
-        <v>90817</v>
+        <v>90820</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>122569536</v>
       </c>
       <c r="B16" t="n">
-        <v>79951</v>
+        <v>79954</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -2402,7 +2402,7 @@
         <v>122492226</v>
       </c>
       <c r="B15" t="n">
-        <v>90923</v>
+        <v>90927</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>122569536</v>
       </c>
       <c r="B16" t="n">
-        <v>80056</v>
+        <v>80060</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2616,6 +2616,258 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123763685</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79862</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norreda torp, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>663005</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6634281</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Högt upp på stammens östsida. Samma ek som hyser kärnticka.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123763655</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90966</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>883</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kärnticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Inocutis dryophila</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Berk.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norreda torp, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>663005</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6634281</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Känd förekomst, två gamla frk</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -2618,10 +2618,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123763685</v>
+        <v>123763655</v>
       </c>
       <c r="B17" t="n">
-        <v>79862</v>
+        <v>90971</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>883</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kärnticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis dryophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Högt upp på stammens östsida. Samma ek som hyser kärnticka.</t>
+          <t>Känd förekomst, två gamla frk</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2744,10 +2744,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123763655</v>
+        <v>123763685</v>
       </c>
       <c r="B18" t="n">
-        <v>90966</v>
+        <v>79867</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2756,25 +2756,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>883</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kärnticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Inocutis dryophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Känd förekomst, två gamla frk</t>
+          <t>Högt upp på stammens östsida. Samma ek som hyser kärnticka.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2399,10 +2399,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122492226</v>
+        <v>122569536</v>
       </c>
       <c r="B15" t="n">
-        <v>90927</v>
+        <v>80060</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2415,37 +2415,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>883</v>
+        <v>228430</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kärnticka</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Inocutis dryophila</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk.) Fiasson &amp; Niemelä</t>
+          <t>(Huds.) A.Massal.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norreda torp, Upl</t>
+          <t>Norredatorp, Norredatorp, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>662997</v>
+        <v>662958</v>
       </c>
       <c r="R15" t="n">
-        <v>6634280</v>
+        <v>6634243</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2469,17 +2469,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Känd lokal</t>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2494,22 +2499,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122569536</v>
+        <v>123763655</v>
       </c>
       <c r="B16" t="n">
-        <v>80060</v>
+        <v>90973</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2522,34 +2527,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228430</v>
+        <v>883</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Kärnticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Inocutis dryophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
+          <t>(Berk.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norredatorp, Norredatorp, Upl</t>
+          <t>Norreda torp, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>662958</v>
+        <v>663005</v>
       </c>
       <c r="R16" t="n">
-        <v>6634243</v>
+        <v>6634281</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2576,22 +2584,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:21</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:21</t>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Känd förekomst, två gamla frk</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2600,28 +2603,44 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123763655</v>
+        <v>123763685</v>
       </c>
       <c r="B17" t="n">
-        <v>90971</v>
+        <v>79869</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2630,25 +2649,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>883</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kärnticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Inocutis dryophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2701,7 +2720,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Känd förekomst, två gamla frk</t>
+          <t>Högt upp på stammens östsida. Samma ek som hyser kärnticka.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2741,132 +2760,6 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>123763685</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79867</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Norreda torp, Upl</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>663005</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6634281</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Knivsta</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Lagga</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Högt upp på stammens östsida. Samma ek som hyser kärnticka.</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Björn Bråvander</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Björn Bråvander</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -2511,10 +2511,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123763655</v>
+        <v>123763685</v>
       </c>
       <c r="B16" t="n">
-        <v>90973</v>
+        <v>79869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>883</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kärnticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Inocutis dryophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Känd förekomst, två gamla frk</t>
+          <t>Högt upp på stammens östsida. Samma ek som hyser kärnticka.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2637,10 +2637,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123763685</v>
+        <v>123763655</v>
       </c>
       <c r="B17" t="n">
-        <v>79869</v>
+        <v>90973</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2649,25 +2649,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>883</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kärnticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis dryophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Högt upp på stammens östsida. Samma ek som hyser kärnticka.</t>
+          <t>Känd förekomst, två gamla frk</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -2511,10 +2511,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123763685</v>
+        <v>123763655</v>
       </c>
       <c r="B16" t="n">
-        <v>79869</v>
+        <v>90973</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>883</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kärnticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis dryophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Högt upp på stammens östsida. Samma ek som hyser kärnticka.</t>
+          <t>Känd förekomst, två gamla frk</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2637,10 +2637,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123763655</v>
+        <v>123763685</v>
       </c>
       <c r="B17" t="n">
-        <v>90973</v>
+        <v>79869</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2649,25 +2649,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>883</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kärnticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Inocutis dryophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Känd förekomst, två gamla frk</t>
+          <t>Högt upp på stammens östsida. Samma ek som hyser kärnticka.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -2511,10 +2511,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123763655</v>
+        <v>123763685</v>
       </c>
       <c r="B16" t="n">
-        <v>90995</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>883</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kärnticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Inocutis dryophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Känd förekomst, två gamla frk</t>
+          <t>Högt upp på stammens östsida. Samma ek som hyser kärnticka.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2637,10 +2637,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123763685</v>
+        <v>123763655</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>90995</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2649,25 +2649,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>883</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kärnticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis dryophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Högt upp på stammens östsida. Samma ek som hyser kärnticka.</t>
+          <t>Känd förekomst, två gamla frk</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16822280</v>
+        <v>75954941</v>
       </c>
       <c r="B2" t="n">
-        <v>5402</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101377</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lagga kyrka, 4,1 km NO-ut, Upl</t>
+          <t>Norreda torp, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662942.7254555774</v>
+        <v>662894</v>
       </c>
       <c r="R2" t="n">
-        <v>6634226.315354125</v>
+        <v>6634202</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-06-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnaghål.</t>
+          <t>2004-06-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,101 +757,65 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Pär Eriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson, Åke Lindelöw</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16823135</v>
+        <v>111424406</v>
       </c>
       <c r="B3" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lagga kyrka, 4,1 km NO-ut, Upl</t>
+          <t>Norrsjön, Norrsjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662915.731950364</v>
+        <v>662973</v>
       </c>
       <c r="R3" t="n">
-        <v>6634220.598178662</v>
+        <v>6634316</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,22 +842,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,55 +868,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Ved # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson, Åke Lindelöw</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75511822</v>
+        <v>63600285</v>
       </c>
       <c r="B4" t="n">
-        <v>89375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,22 +914,24 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norreda torp, Upl</t>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662990.0182534709</v>
+        <v>662997</v>
       </c>
       <c r="R4" t="n">
-        <v>6634286.81535548</v>
+        <v>6634280</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1047,27 +958,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2007-08-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2007-08-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på ek vid Norreda torp</t>
+          <t>1 färskt + 2 fjolårs-ex. på levande ek, omkr. 292 cm. Samma träd och troligen samma svampindivid som den avbildade kärntickan i Ryman &amp; Holmåsens bok, fotograferad i aug. 1980. Svampen var dock känd från lokalen (trädet?) redan 1965 av Ingvar Nordin.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1076,78 +977,85 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gårdsmiljö.</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Levande ek. # Skogsek</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Pär Eriksson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pär Eriksson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75749864</v>
+        <v>75511822</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>883</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kärnticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis dryophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+          <t>Norreda torp, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662966.8437196139</v>
+        <v>662990</v>
       </c>
       <c r="R5" t="n">
-        <v>6634320.550637645</v>
+        <v>6634287</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1174,27 +1082,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2006-02-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-08-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2006-02-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-08-16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ca. 35 dm2 på stammen av levande ek, omkr. 187 cm.</t>
+          <t>på ek vid Norreda torp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1203,87 +1101,67 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Skogsek</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stammen av levande ek. # Skogsek</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Pär Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Pär Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>75749863</v>
+        <v>123763655</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>883</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kärnticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis dryophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Berk.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+          <t>Norreda torp, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>662985.4747768191</v>
+        <v>663005</v>
       </c>
       <c r="R6" t="n">
-        <v>6634321.3682292</v>
+        <v>6634281</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1310,27 +1188,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2006-02-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2006-02-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca. 15 dm2 på stammen av levande asp, omkr. 157 cm.</t>
+          <t>Känd förekomst, två gamla frk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1339,87 +1207,80 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Asp</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stammen av levande asp. # Asp</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>75749866</v>
+        <v>107822800</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
+          <t>Norredatorp, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>662997.398841615</v>
+        <v>662939</v>
       </c>
       <c r="R7" t="n">
-        <v>6634279.584385687</v>
+        <v>6634219</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1446,27 +1307,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2004-07-04</t>
+          <t>2023-04-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2004-07-04</t>
+          <t>2023-04-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 dm2 på stammen av levande ek, omkr. 292 cm.</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1478,84 +1334,79 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Skogsek</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stammen av levande ek. # Skogsek</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75749865</v>
+        <v>123954319</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+          <t>Norreda torp S, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>662967.9466331659</v>
+        <v>662934</v>
       </c>
       <c r="R8" t="n">
-        <v>6634295.416270734</v>
+        <v>6634214</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1582,27 +1433,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2006-02-03</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2006-02-03</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca. 6 dm2 på stammen av levande asp, omkr. 129 cm.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1611,86 +1457,83 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Asp</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stammen av levande asp. # Asp</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Åke Berg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Åke Berg, Håkan Lernefalk, Niklas Hjort</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>75811296</v>
+        <v>107763592</v>
       </c>
       <c r="B9" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+          <t>Norredatorp, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>662944.9565136041</v>
+        <v>662986</v>
       </c>
       <c r="R9" t="n">
-        <v>6634232.960888843</v>
+        <v>6634226</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1714,27 +1557,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2006-02-03</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2006-02-03</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gnagspår och kläckhål i barken på levande gran, omkr. 184 cm.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1745,68 +1583,53 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>63600285</v>
+        <v>62588870</v>
       </c>
       <c r="B10" t="n">
-        <v>89375</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>883</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kärnticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Inocutis dryophila</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1816,14 +1639,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662997.398841615</v>
+        <v>662849</v>
       </c>
       <c r="R10" t="n">
-        <v>6634279.584385687</v>
+        <v>6634191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1850,27 +1673,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2004-07-04</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-02-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2004-07-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-02-21</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1 färskt + 2 fjolårs-ex. på levande ek, omkr. 292 cm. Samma träd och troligen samma svampindivid som den avbildade kärntickan i Ryman &amp; Holmåsens bok, fotograferad i aug. 1980. Svampen var dock känd från lokalen (trädet?) redan 1965 av Ingvar Nordin.</t>
+          <t>2 ex. på levande asp, omkr. 105 cm.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1882,19 +1695,14 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gårdsmiljö.</t>
-        </is>
-      </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Skogsek</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Levande ek. # Skogsek</t>
+          <t>Levande asp. # Asp</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1912,54 +1720,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104370922</v>
+        <v>107763498</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norredatorp, Knivsta, Upl</t>
+          <t>Norredatorp, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>663003.2649096679</v>
+        <v>662983</v>
       </c>
       <c r="R11" t="n">
-        <v>6634283.871116477</v>
+        <v>6634209</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1983,22 +1786,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-10-29</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-29</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2009,85 +1812,65 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Lindell</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Lindell</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107763699</v>
+        <v>111424396</v>
       </c>
       <c r="B12" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2667</v>
+        <v>1619</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Apelticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Aurantiporus fissilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norredatorp, Upl</t>
+          <t>Norrsjön, Norrsjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>662990.7137316827</v>
+        <v>662973</v>
       </c>
       <c r="R12" t="n">
-        <v>6634236.479695288</v>
+        <v>6634316</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2111,22 +1894,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-04-02</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-04-02</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar på två träd ett stående dött träd och en låga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2137,6 +1925,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2146,58 +1949,54 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111424396</v>
+        <v>16822347</v>
       </c>
       <c r="B13" t="n">
-        <v>89816</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1619</v>
+        <v>2014</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Apelticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Aurantiporus fissilis</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrsjön (Norrsjön), Upl</t>
+          <t>Lagga kyrka, 4,1 km NO-ut, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>662972.5812136804</v>
+        <v>662951</v>
       </c>
       <c r="R13" t="n">
-        <v>6634316.269522307</v>
+        <v>6634214</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2224,27 +2023,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar på två träd ett stående dött träd och en låga.</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2253,6 +2037,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2266,74 +2051,78 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson, Åke Lindelöw</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111424406</v>
+        <v>107763699</v>
       </c>
       <c r="B14" t="n">
-        <v>90151</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>366</v>
+        <v>2667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrsjön (Norrsjön), Upl</t>
+          <t>Norredatorp, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>662972.5812136804</v>
+        <v>662991</v>
       </c>
       <c r="R14" t="n">
-        <v>6634316.269522307</v>
+        <v>6634237</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2357,22 +2146,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2392,57 +2181,52 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122569536</v>
+        <v>62588862</v>
       </c>
       <c r="B15" t="n">
-        <v>80060</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228430</v>
+        <v>4660</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norredatorp, Norredatorp, Upl</t>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>662958</v>
+        <v>662887</v>
       </c>
       <c r="R15" t="n">
-        <v>6634243</v>
+        <v>6634198</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2469,22 +2253,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:21</t>
+          <t>2006-02-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:21</t>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På levande asp, omkr. 112 cm.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2495,69 +2274,71 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Levande asp. # Asp</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123763685</v>
+        <v>62588798</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6457</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norreda torp, Upl</t>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>663005</v>
+        <v>662877</v>
       </c>
       <c r="R16" t="n">
-        <v>6634281</v>
+        <v>6634205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2584,17 +2365,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2006-02-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2006-02-21</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Högt upp på stammens östsida. Samma ek som hyser kärnticka.</t>
+          <t>På levande asp, omkr. 102 cm.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2603,87 +2384,82 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Stammen av levande asp. # Asp</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123763655</v>
+        <v>62588814</v>
       </c>
       <c r="B17" t="n">
-        <v>90995</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>883</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kärnticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Inocutis dryophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norreda torp, Upl</t>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>663005</v>
+        <v>662867</v>
       </c>
       <c r="R17" t="n">
-        <v>6634281</v>
+        <v>6634196</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2710,17 +2486,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2006-02-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2006-02-21</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Känd förekomst, två gamla frk</t>
+          <t>2 dm2 på bark på asphögstubbe, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2729,37 +2505,2087 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Bark på asphögstubbe. # Asp</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>62588815</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>662876</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6634188</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca. 20 dm2 på bark på asphögstubbe, omkr. 86 cm.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark på asphögstubbe. # Asp</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>62588823</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>662877</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6634205</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2 dm2 på levande asp, omkr. 102 cm.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>75749863</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>662985</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6634321</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca. 15 dm2 på stammen av levande asp, omkr. 157 cm.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>75749864</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>662967</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6634321</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca. 35 dm2 på stammen av levande ek, omkr. 187 cm.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>75749865</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>662968</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6634295</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ca. 6 dm2 på stammen av levande asp, omkr. 129 cm.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>75749866</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>662997</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6634280</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2004-07-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2004-07-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 dm2 på stammen av levande ek, omkr. 292 cm.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>87741083</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norredatorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>663006</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6634284</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-08-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-08-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Korall</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Korall</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>104370922</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norredatorp, Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>663003</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6634283</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-10-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-10-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johan Lindell</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Johan Lindell</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123763685</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norreda torp, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>663005</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6634281</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Högt upp på stammens östsida. Samma ek som hyser kärnticka.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>Björn Bråvander</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>Björn Bråvander</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>62588848</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>662847</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6634186</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>0,5 dm2 på levande asp, omkr. 128 cm.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>16822345</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,1 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>662951</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6634214</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2014-09-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2014-09-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Ved # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson, Åke Lindelöw</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>16823135</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,1 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>662916</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6634221</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2014-09-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2014-09-07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Ved # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson, Åke Lindelöw</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>16822343</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,1 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>662951</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6634214</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2014-09-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2014-09-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Ved # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson, Åke Lindelöw</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>16822280</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5471</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>101377</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Stekelbock</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Necydalis major</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,1 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>662943</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6634226</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2014-09-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2014-09-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Gnaghål.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson, Åke Lindelöw</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>16823137</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,1 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>662914</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6634203</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2014-09-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2014-09-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Ved # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson, Åke Lindelöw</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>75811296</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>662945</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6634233</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gnagspår och kläckhål i barken på levande gran, omkr. 184 cm.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122569536</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80657</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228430</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Blastenia relicta</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Arup &amp; Vondrák</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Norredatorp, Norredatorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>662958</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6634243</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75954941</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111424406</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63600285</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75511822</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763655</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107822800</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1488,6 +1523,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123954319</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1596,6 +1636,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107763592</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1717,6 +1762,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588870</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1825,6 +1875,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107763498</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1953,6 +2008,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111424396</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2077,6 +2137,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16822347</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2185,6 +2250,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107763699</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2297,6 +2367,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588862</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2409,6 +2484,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588798</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2530,6 +2610,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588814</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2651,6 +2736,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588815</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2772,6 +2862,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588823</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2893,6 +2988,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75749863</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3014,6 +3114,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75749864</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3135,6 +3240,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75749865</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3256,6 +3366,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75749866</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3357,6 +3472,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87741083</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3470,6 +3590,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104370922</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3591,6 +3716,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763685</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3712,6 +3842,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588848</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3842,6 +3977,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16822345</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3972,6 +4112,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16823135</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4102,6 +4247,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16822343</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4237,6 +4387,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16822280</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4367,6 +4522,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16823137</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4484,6 +4644,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75811296</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4586,8 +4751,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122569536</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>